--- a/data/trending_integrated_20260915_15.xlsx
+++ b/data/trending_integrated_20260915_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3360</v>
+        <v>3340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.98%</t>
+          <t>'+67.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G2" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2585</v>
+        <v>1990</v>
       </c>
       <c r="K2" t="n">
-        <v>2725</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3360</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2690</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>125621270000</v>
+        <v>132877000000</v>
       </c>
       <c r="P2" t="n">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>966</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-389000</v>
@@ -676,7 +676,7 @@
         <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>65940988385</v>
+        <v>66051760435</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 보안 테마 강세. 클래리티 법안 통과 여부가 주가에 영향을 줄 것으로 예상. 10000원 돌파 기대.</t>
+          <t>양자 보안 관련 기대감. 클래리티 법안 통과 여부에 따른 주가 변동성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -762,13 +762,13 @@
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48909549239</v>
+        <v>48958052259</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11730</v>
+        <v>11620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+26.54%</t>
+          <t>'+25.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>208439458355</v>
+        <v>212737914475</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24900</v>
+        <v>24800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.70%</t>
+          <t>'+13.24%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
         <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>223018926350</v>
+        <v>224432156275</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1023,123 +1023,123 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51500</v>
+        <v>3660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.74%</t>
+          <t>'+7.65%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.18</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>203</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>615</v>
+        <v>231</v>
       </c>
       <c r="H7" t="n">
-        <v>13.97</v>
+        <v>0.83</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>47800</v>
+        <v>3400</v>
       </c>
       <c r="K7" t="n">
-        <v>47300</v>
+        <v>3450</v>
       </c>
       <c r="L7" t="n">
-        <v>54600</v>
+        <v>4080</v>
       </c>
       <c r="M7" t="n">
-        <v>46400</v>
+        <v>3445</v>
       </c>
       <c r="N7" t="n">
-        <v>14.15</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>95358656475</v>
+        <v>155856455497</v>
       </c>
       <c r="P7" t="n">
-        <v>108900</v>
+        <v>4335</v>
       </c>
       <c r="Q7" t="n">
-        <v>18230</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>70000</v>
+        <v>-32000</v>
       </c>
       <c r="S7" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
+          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
+          <t>['상승파동', '대장', '세력']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35350</v>
+        <v>51300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.12%</t>
+          <t>'+7.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>205</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="G8" t="n">
-        <v>323</v>
+        <v>621</v>
       </c>
       <c r="H8" t="n">
-        <v>14.93</v>
+        <v>13.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>33000</v>
+        <v>47800</v>
       </c>
       <c r="K8" t="n">
-        <v>32750</v>
+        <v>47300</v>
       </c>
       <c r="L8" t="n">
-        <v>37200</v>
+        <v>54600</v>
       </c>
       <c r="M8" t="n">
-        <v>32750</v>
+        <v>46400</v>
       </c>
       <c r="N8" t="n">
-        <v>15.06</v>
+        <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>56066404250</v>
+        <v>96989209175</v>
       </c>
       <c r="P8" t="n">
-        <v>50400</v>
+        <v>108900</v>
       </c>
       <c r="Q8" t="n">
-        <v>23650</v>
+        <v>18230</v>
       </c>
       <c r="R8" t="n">
-        <v>349000</v>
+        <v>70000</v>
       </c>
       <c r="S8" t="n">
-        <v>109000</v>
+        <v>65000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
+          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,82 +1195,82 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3630</v>
+        <v>35350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.76%</t>
+          <t>'+7.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G9" t="n">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="H9" t="n">
-        <v>0.83</v>
+        <v>14.93</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3400</v>
+        <v>33000</v>
       </c>
       <c r="K9" t="n">
-        <v>3450</v>
+        <v>32750</v>
       </c>
       <c r="L9" t="n">
-        <v>4080</v>
+        <v>37200</v>
       </c>
       <c r="M9" t="n">
-        <v>3445</v>
+        <v>32750</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>15.06</v>
       </c>
       <c r="O9" t="n">
-        <v>154946734985</v>
+        <v>58272304750</v>
       </c>
       <c r="P9" t="n">
-        <v>4335</v>
+        <v>50400</v>
       </c>
       <c r="Q9" t="n">
-        <v>1246</v>
+        <v>23650</v>
       </c>
       <c r="R9" t="n">
-        <v>-32000</v>
+        <v>349000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>긍정적인 상승 파동 기대감 및 세력 움직임 언급. "날아간다", "대장" 등 긍정적 표현.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상승파동', '대장', '세력']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32400</v>
+        <v>32300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+6.75%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F10" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G10" t="n">
-        <v>1033</v>
+        <v>1050</v>
       </c>
       <c r="H10" t="n">
         <v>17.5</v>
@@ -1346,7 +1346,7 @@
         <v>17.55</v>
       </c>
       <c r="O10" t="n">
-        <v>17708321225</v>
+        <v>18267512525</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 기대감 및 우려 공존. 개인 투자자들의 매매 동향 언급.</t>
+          <t>FDA 승인 기대감 및 주가 변동성. 기관/외인 매도.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['담관암', 'FDA승인', '주가전망']</t>
+          <t>['FDA승인', '담관암', '기관외인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14770</v>
+        <v>14750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+4.54%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H11" t="n">
         <v>10.75</v>
@@ -1438,7 +1438,7 @@
         <v>10.69</v>
       </c>
       <c r="O11" t="n">
-        <v>126004573385</v>
+        <v>127801671645</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142100</v>
+        <v>10640</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.95%</t>
+          <t>'+3.60%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="F12" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="G12" t="n">
-        <v>351</v>
+        <v>490</v>
       </c>
       <c r="H12" t="n">
-        <v>15.81</v>
+        <v>17.93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>136700</v>
+        <v>10270</v>
       </c>
       <c r="K12" t="n">
-        <v>139500</v>
+        <v>11000</v>
       </c>
       <c r="L12" t="n">
-        <v>144100</v>
+        <v>11650</v>
       </c>
       <c r="M12" t="n">
-        <v>138200</v>
+        <v>10010</v>
       </c>
       <c r="N12" t="n">
-        <v>15.76</v>
+        <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>124017876350</v>
+        <v>357082426100</v>
       </c>
       <c r="P12" t="n">
-        <v>164700</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>87700</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>-3000</v>
+        <v>181000</v>
       </c>
       <c r="S12" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>합병 반대 의견 및 정유/배터리 업황 슈퍼 사이클 기대. 주가 변동성에 대한 우려.</t>
+          <t>아이온큐 급등에 따른 광통신 테마 기대감. 기타법인 매수 유입.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['합병반대', '정유주', '배터리']</t>
+          <t>['광통신', '아이온큐', '기타법인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10630</v>
+        <v>141600</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.51%</t>
+          <t>'+3.58%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>490</v>
+        <v>359</v>
       </c>
       <c r="H13" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K13" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L13" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M13" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N13" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O13" t="n">
-        <v>354492336110</v>
+        <v>126854797150</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R13" t="n">
-        <v>181000</v>
+        <v>-3000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이온큐 급등 및 기타법인 매수세 유입으로 인한 기대감 고조. 트럼프 발언에 따른 AI 성장 기대.</t>
+          <t>합병 반대 의견 및 주가 하락 우려. 정유/배터리 업황.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아이온큐', 'AI', '기타법인']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,130 +1660,130 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19240</v>
+        <v>15000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.56%</t>
+          <t>'+2.32%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="H14" t="n">
-        <v>10.53</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18760</v>
+        <v>14660</v>
       </c>
       <c r="K14" t="n">
-        <v>18440</v>
+        <v>14980</v>
       </c>
       <c r="L14" t="n">
-        <v>19330</v>
+        <v>15460</v>
       </c>
       <c r="M14" t="n">
-        <v>18120</v>
+        <v>14330</v>
       </c>
       <c r="N14" t="n">
-        <v>10.55</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>78262849460</v>
+        <v>66544058380</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>36200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>8920</v>
       </c>
       <c r="R14" t="n">
-        <v>23000</v>
+        <v>-7000</v>
       </c>
       <c r="S14" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>이란 관련 지정학적 리스크에 따른 유가 상승 기대. 외인 수급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['유가', '이란', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15000</v>
+        <v>17580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.21%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.17</v>
+        <v>-2.35</v>
       </c>
       <c r="E15" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F15" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G15" t="n">
-        <v>466</v>
+        <v>346</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14660</v>
+        <v>17200</v>
       </c>
       <c r="K15" t="n">
-        <v>14980</v>
+        <v>17220</v>
       </c>
       <c r="L15" t="n">
-        <v>15460</v>
+        <v>18390</v>
       </c>
       <c r="M15" t="n">
-        <v>14330</v>
+        <v>16600</v>
       </c>
       <c r="N15" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>65854300905</v>
+        <v>197545251540</v>
       </c>
       <c r="P15" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>-7000</v>
+        <v>-33000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크 부각에 따른 유가 상승 및 급등 전망.</t>
+          <t>미국 양자 보안주 테마와 연관된 급등 가능성 언급, 주가 흐름에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학']</t>
+          <t>['양자 보안', '신고가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10130</v>
+        <v>19140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>172</v>
+        <v>471</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6</v>
+        <v>10.53</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9990</v>
+        <v>18760</v>
       </c>
       <c r="K16" t="n">
-        <v>10110</v>
+        <v>18440</v>
       </c>
       <c r="L16" t="n">
-        <v>11390</v>
+        <v>19330</v>
       </c>
       <c r="M16" t="n">
-        <v>9980</v>
+        <v>18120</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>10.55</v>
       </c>
       <c r="O16" t="n">
-        <v>161068273275</v>
+        <v>81630948135</v>
       </c>
       <c r="P16" t="n">
-        <v>15960</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>3500</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-13000</v>
+        <v>23000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가조작', '저질약품']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,99 +1936,99 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17330</v>
+        <v>10130</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+1.40%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-2.35</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>112</v>
       </c>
       <c r="F17" t="n">
-        <v>111</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="H17" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17200</v>
+        <v>9990</v>
       </c>
       <c r="K17" t="n">
-        <v>17220</v>
+        <v>10110</v>
       </c>
       <c r="L17" t="n">
-        <v>18390</v>
+        <v>11390</v>
       </c>
       <c r="M17" t="n">
-        <v>16600</v>
+        <v>9980</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>195349820100</v>
+        <v>162002180095</v>
       </c>
       <c r="P17" t="n">
-        <v>30550</v>
+        <v>15960</v>
       </c>
       <c r="Q17" t="n">
-        <v>6100</v>
+        <v>3500</v>
       </c>
       <c r="R17" t="n">
-        <v>-33000</v>
+        <v>-13000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 테마와 연관된 급등 가능성 언급, 주가 흐름에 대한 아쉬움 표출.</t>
+          <t>부정적인 언급과 함께 주가 조작 의혹 제기. "저질약품", "최악" 등 부정적 표현 다수.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['양자 보안', '신고가']</t>
+          <t>['주가조작', '저질약품']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6880</v>
+        <v>6890</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.29%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>45843574890</v>
+        <v>46125309210</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>247500</v>
+        <v>247250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.60%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G19" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H19" t="n">
         <v>46.57</v>
@@ -2174,7 +2174,7 @@
         <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>2417645753000</v>
+        <v>2463214733750</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>네이버 증권 화면 불편함 및 금리 인상 선반영 전망. 정치적 언급 다수.</t>
+          <t>네이버 증권 화면 불편함 및 정치 관련 언급. 금리 인상 불확실성 해소 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리인상', '증권화면', '정치']</t>
+          <t>['금리인상', '네이버증권', '정치']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,31 +2219,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1684000</v>
+        <v>86200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.77%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>303</v>
       </c>
       <c r="F20" t="n">
-        <v>456</v>
+        <v>155</v>
       </c>
       <c r="G20" t="n">
-        <v>1434</v>
+        <v>982</v>
       </c>
       <c r="H20" t="n">
-        <v>50.27</v>
+        <v>23.45</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1697000</v>
+        <v>87000</v>
       </c>
       <c r="K20" t="n">
-        <v>1690000</v>
+        <v>86200</v>
       </c>
       <c r="L20" t="n">
-        <v>1729000</v>
+        <v>86800</v>
       </c>
       <c r="M20" t="n">
-        <v>1671000</v>
+        <v>84200</v>
       </c>
       <c r="N20" t="n">
-        <v>50.47</v>
+        <v>23.56</v>
       </c>
       <c r="O20" t="n">
-        <v>3893662049000</v>
+        <v>167015692900</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>325000</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-297000</v>
+        <v>-220000</v>
       </c>
       <c r="S20" t="n">
-        <v>-104000</v>
+        <v>-152000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>AI 및 금리 이슈, 중국 메모리 이슈 등 다양한 변수로 인한 투자 심리 위축. 네이버 증권 화면 불편함 언급.</t>
+          <t>원전 사업 확대 기대감 및 수주 증가 전망. 에너지 독립 관련 수혜.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['AI이슈', '금리인상', '메모리']</t>
+          <t>['원전', '수주', '에너지독립']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86200</v>
+        <v>1679000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="E21" t="n">
-        <v>290</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
-        <v>150</v>
+        <v>448</v>
       </c>
       <c r="G21" t="n">
-        <v>958</v>
+        <v>1444</v>
       </c>
       <c r="H21" t="n">
-        <v>23.45</v>
+        <v>50.27</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>87000</v>
+        <v>1697000</v>
       </c>
       <c r="K21" t="n">
-        <v>86200</v>
+        <v>1690000</v>
       </c>
       <c r="L21" t="n">
-        <v>86800</v>
+        <v>1729000</v>
       </c>
       <c r="M21" t="n">
-        <v>84200</v>
+        <v>1671000</v>
       </c>
       <c r="N21" t="n">
-        <v>23.56</v>
+        <v>50.47</v>
       </c>
       <c r="O21" t="n">
-        <v>159510557700</v>
+        <v>3992322244000</v>
       </c>
       <c r="P21" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q21" t="n">
-        <v>57000</v>
+        <v>325000</v>
       </c>
       <c r="R21" t="n">
-        <v>-220000</v>
+        <v>-297000</v>
       </c>
       <c r="S21" t="n">
-        <v>-152000</v>
+        <v>-104000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 관련 ETF 추가 출시 및 긍정적인 시나리오가 제시되는 가운데, 엑스에너지의 급등이 두산에너빌리티의 상승 기대감을 높임. 유가 상승에 따른 에너지 독립 필요성이 부각됨.</t>
+          <t>AI 이슈 및 금리 변동성에 따른 주가 불안정. JP모건 AI 인프라 대출 중단 소식.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', 'ETF', '유가']</t>
+          <t>['AI', '금리', 'JP모건']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2418,13 +2418,13 @@
         <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G22" t="n">
-        <v>1006</v>
+        <v>1040</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>100471095500</v>
+        <v>106375766000</v>
       </c>
       <c r="P22" t="n">
         <v>426000</v>
@@ -2495,70 +2495,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8660</v>
+        <v>14130</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G23" t="n">
-        <v>494</v>
+        <v>563</v>
       </c>
       <c r="H23" t="n">
-        <v>27.16</v>
+        <v>1.8</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>8850</v>
+        <v>14490</v>
       </c>
       <c r="K23" t="n">
-        <v>8750</v>
+        <v>14410</v>
       </c>
       <c r="L23" t="n">
-        <v>8840</v>
+        <v>14600</v>
       </c>
       <c r="M23" t="n">
-        <v>8630</v>
+        <v>13930</v>
       </c>
       <c r="N23" t="n">
-        <v>27.16</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>26034892370</v>
+        <v>64976524795</v>
       </c>
       <c r="P23" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R23" t="n">
-        <v>-565000</v>
+        <v>68000</v>
       </c>
       <c r="S23" t="n">
-        <v>7000</v>
+        <v>-2000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>하반기 목표주가 11000원으로 하향 조정된 가운데, 연기금은 순매수를 이어가고 있으나 주가는 3주 연속 음봉을 기록하며 부진한 흐름을 보임. 일부에서는 PBR 평가 방식에 대한 의문을 제기하며 저평가 상태라고 주장.</t>
+          <t>머니투데이 방송 노출 효과 및 광통신 테마 기대. AI, 금리 등 거시 변수.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['목표주가', '연기금', 'PBR']</t>
+          <t>['광통신', '테마', 'AI']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14150</v>
+        <v>8620</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.35%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8</v>
+        <v>27.16</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>14490</v>
+        <v>8850</v>
       </c>
       <c r="K24" t="n">
-        <v>14410</v>
+        <v>8750</v>
       </c>
       <c r="L24" t="n">
-        <v>14600</v>
+        <v>8840</v>
       </c>
       <c r="M24" t="n">
-        <v>13930</v>
+        <v>8610</v>
       </c>
       <c r="N24" t="n">
-        <v>1.88</v>
+        <v>27.16</v>
       </c>
       <c r="O24" t="n">
-        <v>64328537410</v>
+        <v>27555482325</v>
       </c>
       <c r="P24" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q24" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R24" t="n">
-        <v>68000</v>
+        <v>-565000</v>
       </c>
       <c r="S24" t="n">
-        <v>-2000</v>
+        <v>7000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>방송 홍보 및 15000원 이상 상승 기대감, 광전자와의 비교 속 키 맞추기 움직임.</t>
+          <t>목표주가 하향 및 실적 부진 우려. 공매도 세력 활동.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['대한광통신', '광전자']</t>
+          <t>['목표주가', '실적', '공매도']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4140</v>
+        <v>4105</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-4.28%</t>
+          <t>'-5.09%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>75082527155</v>
+        <v>75882356047</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20800</v>
+        <v>20750</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-5.88%</t>
+          <t>'-6.11%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F26" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G26" t="n">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>74126655625</v>
+        <v>74895014600</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_15.xlsx
+++ b/data/trending_integrated_20260915_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+67.84%</t>
+          <t>'+29.98%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1990</v>
+        <v>2585</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2725</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2690</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>132877000000</v>
+        <v>133837891585</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="R2" t="n">
         <v>-389000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성과 4381억 규모 계약 체결, 광통신 및 양자 관련 테마주로 급등 전망.</t>
+          <t>양자, 광통신, 보안 테마 관련주로 급등세. 신규 양산 준비 중이라는 언급과 함께 1만원 목표가 제시. 긍정적인 투자 심리 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['계약체결', '광통신', '양자']</t>
+          <t>['양자', '광통신']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>66051760435</v>
+        <v>66130900455</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -762,13 +762,13 @@
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48958052259</v>
+        <v>48978893809</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11620</v>
+        <v>11790</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+25.35%</t>
+          <t>'+27.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F5" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G5" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>212737914475</v>
+        <v>220807414470</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모치료제 관련 특허 및 장기지속형 주사제 기술 보유. 품절주 및 높은 유동물량으로 인한 급등 기대.</t>
+          <t>탈모 치료제 특허 및 세계 최초 타이틀에 대한 기대감이 높음. 품절주로서 급등 가능성 언급. 긍정적인 기대 심리 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모치료제', '특허', '유동물량']</t>
+          <t>['탈모치료제', '특허']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24800</v>
+        <v>24950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.24%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
         <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>224432156275</v>
+        <v>226726295400</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3660</v>
+        <v>3685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.65%</t>
+          <t>'+8.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>155856455497</v>
+        <v>158630605516</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51300</v>
+        <v>51600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.32%</t>
+          <t>'+7.95%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F8" t="n">
         <v>101</v>
       </c>
       <c r="G8" t="n">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="H8" t="n">
         <v>13.97</v>
@@ -1162,7 +1162,7 @@
         <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>96989209175</v>
+        <v>98296235025</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1207,79 +1207,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대제철</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35350</v>
+        <v>32500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.12%</t>
+          <t>'+7.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="F9" t="n">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="G9" t="n">
-        <v>331</v>
+        <v>1077</v>
       </c>
       <c r="H9" t="n">
-        <v>14.93</v>
+        <v>17.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>33000</v>
+        <v>30350</v>
       </c>
       <c r="K9" t="n">
-        <v>32750</v>
+        <v>30250</v>
       </c>
       <c r="L9" t="n">
-        <v>37200</v>
+        <v>32500</v>
       </c>
       <c r="M9" t="n">
-        <v>32750</v>
+        <v>30250</v>
       </c>
       <c r="N9" t="n">
-        <v>15.06</v>
+        <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>58272304750</v>
+        <v>18900239800</v>
       </c>
       <c r="P9" t="n">
-        <v>50400</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>23650</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>349000</v>
+        <v>82000</v>
       </c>
       <c r="S9" t="n">
-        <v>109000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
+          <t>FDA 승인 기대감 및 주가 변동성. 기관/외인 매도.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['PBR', '저평가', '정배열']</t>
+          <t>['FDA승인', '담관암', '기관외인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,91 +1287,91 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>현대제철</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32300</v>
+        <v>35300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+6.43%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>1050</v>
+        <v>331</v>
       </c>
       <c r="H10" t="n">
-        <v>17.5</v>
+        <v>14.93</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>30350</v>
+        <v>33000</v>
       </c>
       <c r="K10" t="n">
-        <v>30250</v>
+        <v>32750</v>
       </c>
       <c r="L10" t="n">
-        <v>32500</v>
+        <v>37200</v>
       </c>
       <c r="M10" t="n">
-        <v>30250</v>
+        <v>32750</v>
       </c>
       <c r="N10" t="n">
-        <v>17.55</v>
+        <v>15.06</v>
       </c>
       <c r="O10" t="n">
-        <v>18267512525</v>
+        <v>60166795575</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>50400</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>23650</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>349000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>109000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 및 주가 변동성. 기관/외인 매도.</t>
+          <t>PBR 0.22, 0.07 등 저평가 지표와 한국거래소의 저PBR 기업 딱지 관련 뉴스를 바탕으로 상승 기대감이 형성됨. 120일선 돌파 등 기술적 지표도 언급됨.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '기관외인']</t>
+          <t>['PBR', '저평가', '정배열']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>004020</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14750</v>
+        <v>14770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.54%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H11" t="n">
         <v>10.75</v>
@@ -1438,7 +1438,7 @@
         <v>10.69</v>
       </c>
       <c r="O11" t="n">
-        <v>127801671645</v>
+        <v>129406184985</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10640</v>
+        <v>141700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.60%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>490</v>
+        <v>363</v>
       </c>
       <c r="H12" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K12" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L12" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M12" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N12" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O12" t="n">
-        <v>357082426100</v>
+        <v>129312554600</v>
       </c>
       <c r="P12" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q12" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R12" t="n">
-        <v>181000</v>
+        <v>-3000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>아이온큐 급등에 따른 광통신 테마 기대감. 기타법인 매수 유입.</t>
+          <t>합병 반대 의견이 존재하나, 정유 및 배터리 섹터의 슈퍼 사이클 기대감도 일부 언급. 주가 하락에 대한 우려와 상승 가능성에 대한 논의 혼재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '아이온큐', '기타법인']</t>
+          <t>['합병', '정유']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>141600</v>
+        <v>10610</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.58%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E13" t="n">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G13" t="n">
-        <v>359</v>
+        <v>494</v>
       </c>
       <c r="H13" t="n">
-        <v>15.81</v>
+        <v>17.93</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>136700</v>
+        <v>10270</v>
       </c>
       <c r="K13" t="n">
-        <v>139500</v>
+        <v>11000</v>
       </c>
       <c r="L13" t="n">
-        <v>144100</v>
+        <v>11650</v>
       </c>
       <c r="M13" t="n">
-        <v>138200</v>
+        <v>10010</v>
       </c>
       <c r="N13" t="n">
-        <v>15.76</v>
+        <v>17.67</v>
       </c>
       <c r="O13" t="n">
-        <v>126854797150</v>
+        <v>359572334330</v>
       </c>
       <c r="P13" t="n">
-        <v>164700</v>
+        <v>22450</v>
       </c>
       <c r="Q13" t="n">
-        <v>87700</v>
+        <v>1760</v>
       </c>
       <c r="R13" t="n">
-        <v>-3000</v>
+        <v>181000</v>
       </c>
       <c r="S13" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>합병 반대 의견 및 주가 하락 우려. 정유/배터리 업황.</t>
+          <t>아이온큐 급등에 따른 광통신 테마 기대감. 기타법인 매수 유입.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['합병', '정유', '배터리']</t>
+          <t>['광통신', '아이온큐', '기타법인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15000</v>
+        <v>14960</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.32%</t>
+          <t>'+2.05%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" t="n">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>66544058380</v>
+        <v>67437556330</v>
       </c>
       <c r="P14" t="n">
         <v>36200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크에 따른 유가 상승 기대. 외인 수급.</t>
+          <t>중동 지역의 지정학적 이슈로 인한 유가 급등 가능성 및 관련 수혜 기대감. 긍정적인 흐름 전망. 유가 관련 논의 활발.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '이란', '지정학적리스크']</t>
+          <t>['유가', '중동']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,184 +1759,184 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17580</v>
+        <v>19130</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.21%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-2.35</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="F15" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>346</v>
+        <v>472</v>
       </c>
       <c r="H15" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17200</v>
+        <v>18760</v>
       </c>
       <c r="K15" t="n">
-        <v>17220</v>
+        <v>18440</v>
       </c>
       <c r="L15" t="n">
-        <v>18390</v>
+        <v>19330</v>
       </c>
       <c r="M15" t="n">
-        <v>16600</v>
+        <v>18120</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>10.55</v>
       </c>
       <c r="O15" t="n">
-        <v>197545251540</v>
+        <v>82855768575</v>
       </c>
       <c r="P15" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-33000</v>
+        <v>23000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 양자 보안주 테마와 연관된 급등 가능성 언급, 주가 흐름에 대한 아쉬움 표출.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['양자 보안', '신고가']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19140</v>
+        <v>17510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.03%</t>
+          <t>'+1.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-2.35</v>
       </c>
       <c r="E16" t="n">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>471</v>
+        <v>350</v>
       </c>
       <c r="H16" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18760</v>
+        <v>17200</v>
       </c>
       <c r="K16" t="n">
-        <v>18440</v>
+        <v>17220</v>
       </c>
       <c r="L16" t="n">
-        <v>19330</v>
+        <v>18390</v>
       </c>
       <c r="M16" t="n">
-        <v>18120</v>
+        <v>16600</v>
       </c>
       <c r="N16" t="n">
-        <v>10.55</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>81630948135</v>
+        <v>198935439450</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R16" t="n">
-        <v>23000</v>
+        <v>-33000</v>
       </c>
       <c r="S16" t="n">
-        <v>29000</v>
+        <v>2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>양자 보안 관련 테마주로 언급되며 신고가 달성. 일부 긍정적인 흐름에 대한 기대와 함께 주가 움직임에 대한 아쉬움도 공존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['양자보안', '신고가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
@@ -1958,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
         <v>174</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>162002180095</v>
+        <v>163977568895</v>
       </c>
       <c r="P17" t="n">
         <v>15960</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6890</v>
+        <v>6900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>46125309210</v>
+        <v>46379308410</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>247250</v>
+        <v>1688000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.53%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="G19" t="n">
-        <v>1385</v>
+        <v>1471</v>
       </c>
       <c r="H19" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,38 +2159,38 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K19" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L19" t="n">
-        <v>252000</v>
+        <v>1729000</v>
       </c>
       <c r="M19" t="n">
-        <v>246000</v>
+        <v>1671000</v>
       </c>
       <c r="N19" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O19" t="n">
-        <v>2463214733750</v>
+        <v>4089931805500</v>
       </c>
       <c r="P19" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q19" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R19" t="n">
-        <v>-368000</v>
+        <v>-297000</v>
       </c>
       <c r="S19" t="n">
-        <v>-565000</v>
+        <v>-104000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>네이버 증권 화면 불편함 및 정치 관련 언급. 금리 인상 불확실성 해소 기대.</t>
+          <t>금리 인상, AI 이슈 등 거시 경제 및 산업 불확실성에 대한 우려가 지배적. 투자 심리 불안정 및 하락 가능성에 대한 논의가 많음.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리인상', '네이버증권', '정치']</t>
+          <t>['금리인상', 'AI이슈']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86200</v>
+        <v>247500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-0.60%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>303</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>155</v>
+        <v>469</v>
       </c>
       <c r="G20" t="n">
-        <v>982</v>
+        <v>1407</v>
       </c>
       <c r="H20" t="n">
-        <v>23.45</v>
+        <v>46.57</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87000</v>
+        <v>249000</v>
       </c>
       <c r="K20" t="n">
-        <v>86200</v>
+        <v>248000</v>
       </c>
       <c r="L20" t="n">
-        <v>86800</v>
+        <v>252000</v>
       </c>
       <c r="M20" t="n">
-        <v>84200</v>
+        <v>246000</v>
       </c>
       <c r="N20" t="n">
-        <v>23.56</v>
+        <v>46.64</v>
       </c>
       <c r="O20" t="n">
-        <v>167015692900</v>
+        <v>2522749670500</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>75900</v>
       </c>
       <c r="R20" t="n">
-        <v>-220000</v>
+        <v>-368000</v>
       </c>
       <c r="S20" t="n">
-        <v>-152000</v>
+        <v>-565000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>원전 사업 확대 기대감 및 수주 증가 전망. 에너지 독립 관련 수혜.</t>
+          <t>정치 관련 언급이 주를 이루며, 일부 증시 환경 변화에 대한 언급이 있으나 구체적인 분석은 부족함. 투자 심리에는 부정적 영향을 줄 수 있음.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지독립']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1679000</v>
+        <v>86200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.06%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="F21" t="n">
-        <v>448</v>
+        <v>157</v>
       </c>
       <c r="G21" t="n">
-        <v>1444</v>
+        <v>1003</v>
       </c>
       <c r="H21" t="n">
-        <v>50.27</v>
+        <v>23.45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1697000</v>
+        <v>87000</v>
       </c>
       <c r="K21" t="n">
-        <v>1690000</v>
+        <v>86200</v>
       </c>
       <c r="L21" t="n">
-        <v>1729000</v>
+        <v>86800</v>
       </c>
       <c r="M21" t="n">
-        <v>1671000</v>
+        <v>84200</v>
       </c>
       <c r="N21" t="n">
-        <v>50.47</v>
+        <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>3992322244000</v>
+        <v>170612923950</v>
       </c>
       <c r="P21" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q21" t="n">
-        <v>325000</v>
+        <v>57000</v>
       </c>
       <c r="R21" t="n">
-        <v>-297000</v>
+        <v>-220000</v>
       </c>
       <c r="S21" t="n">
-        <v>-104000</v>
+        <v>-152000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>AI 이슈 및 금리 변동성에 따른 주가 불안정. JP모건 AI 인프라 대출 중단 소식.</t>
+          <t>원전 사업 확대 기대감 및 수주 증가 전망. 에너지 독립 관련 수혜.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['AI', '금리', 'JP모건']</t>
+          <t>['원전', '수주', '에너지독립']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>222000</v>
+        <v>222500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-1.33%</t>
+          <t>'-1.11%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F22" t="n">
         <v>91</v>
       </c>
       <c r="G22" t="n">
-        <v>1040</v>
+        <v>1070</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>106375766000</v>
+        <v>109657552000</v>
       </c>
       <c r="P22" t="n">
         <v>426000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>머스크 테슬라향 패키징 장비 공급 뉴스 기반 급등 조짐. 공매도 관련 언급 다수.</t>
+          <t>머스크의 테라팹 공급 관련 뉴스가 호재로 작용. 패키징 장비 공급 사실 기반으로 주가 상승 기대감 높음. 긍정적 투자 심리 형성.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['테슬라', '패키징장비', '공매도']</t>
+          <t>['테라팹', '공급']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14130</v>
+        <v>14140</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>64976524795</v>
+        <v>65668290970</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F24" t="n">
         <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="H24" t="n">
         <v>27.16</v>
@@ -2634,7 +2634,7 @@
         <v>27.16</v>
       </c>
       <c r="O24" t="n">
-        <v>27555482325</v>
+        <v>28732683230</v>
       </c>
       <c r="P24" t="n">
         <v>17950</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4105</v>
+        <v>4120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-5.09%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>75882356047</v>
+        <v>76415249547</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2786,13 +2786,13 @@
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F26" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G26" t="n">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>74895014600</v>
+        <v>75905273150</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>

--- a/data/trending_integrated_20260915_15.xlsx
+++ b/data/trending_integrated_20260915_15.xlsx
@@ -578,13 +578,13 @@
         <v>1.34</v>
       </c>
       <c r="E2" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>133837891585</v>
+        <v>133872213985</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>양자, 광통신, 보안 테마 관련주로 급등세. 신규 양산 준비 중이라는 언급과 함께 1만원 목표가 제시. 긍정적인 투자 심리 형성.</t>
+          <t>거래량 급증과 함께 광통신, 양자 관련 테마주로 부각되며 큰 폭의 상승세를 보임.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '광통신']</t>
+          <t>['양자', '광통신', '테마주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
         <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>66130900455</v>
+        <v>67015082895</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자 보안 관련 기대감. 클래리티 법안 통과 여부에 따른 주가 변동성.</t>
+          <t>양자 보안 관련주로 부각되며 주가 상승을 보였으나, 법안 통과 여부에 따라 변동성 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '클래리티', '법안']</t>
+          <t>['양자 보안', '법안 통과', '클래리티']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -768,7 +768,7 @@
         <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>48978893809</v>
+        <v>49002235299</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11790</v>
+        <v>11690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+27.18%</t>
+          <t>'+26.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F5" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>220807414470</v>
+        <v>221969096530</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 특허 및 세계 최초 타이틀에 대한 기대감이 높음. 품절주로서 급등 가능성 언급. 긍정적인 기대 심리 존재.</t>
+          <t>탈모 치료제 특허 및 세계 최초 타이틀에 대한 기대감으로 급등했으나, 변동성도 큰 모습을 보임.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모치료제', '특허']</t>
+          <t>['탈모 치료제', '특허', '품절주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24950</v>
+        <v>25050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.93%</t>
+          <t>'+14.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
         <v>263</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>226726295400</v>
+        <v>227979221250</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3685</v>
+        <v>3680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.38%</t>
+          <t>'+8.24%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>158630605516</v>
+        <v>159149202156</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1162,7 +1162,7 @@
         <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>98296235025</v>
+        <v>99037159425</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>연이은 수주 공시에도 불구하고 주가 상승 미미. 하이퍼스케일러 수주 및 송전망 건설 관련 논의. 공매도 세력에 대한 언급.</t>
+          <t>연이은 대규모 수주 공시에도 불구하고 주가 상승이 더딘 것에 대한 의문과 함께 장기적 상승에 대한 기대감 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['수주 공시', '하이퍼스케일러', '송전망']</t>
+          <t>['수주 공시', '두산퓨얼셀', '수소']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32500</v>
+        <v>32450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.08%</t>
+          <t>'+6.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F9" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G9" t="n">
-        <v>1077</v>
+        <v>1108</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>18900239800</v>
+        <v>19930916700</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35300</v>
+        <v>35150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+6.97%</t>
+          <t>'+6.52%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
         <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H10" t="n">
         <v>14.93</v>
@@ -1346,7 +1346,7 @@
         <v>15.06</v>
       </c>
       <c r="O10" t="n">
-        <v>60166795575</v>
+        <v>61079008375</v>
       </c>
       <c r="P10" t="n">
         <v>50400</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14770</v>
+        <v>14780</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+4.75%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
         <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H11" t="n">
         <v>10.75</v>
@@ -1438,7 +1438,7 @@
         <v>10.69</v>
       </c>
       <c r="O11" t="n">
-        <v>129406184985</v>
+        <v>130307040765</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141700</v>
+        <v>10660</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.66%</t>
+          <t>'+3.80%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="G12" t="n">
-        <v>363</v>
+        <v>497</v>
       </c>
       <c r="H12" t="n">
-        <v>15.81</v>
+        <v>17.93</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>136700</v>
+        <v>10270</v>
       </c>
       <c r="K12" t="n">
-        <v>139500</v>
+        <v>11000</v>
       </c>
       <c r="L12" t="n">
-        <v>144100</v>
+        <v>11650</v>
       </c>
       <c r="M12" t="n">
-        <v>138200</v>
+        <v>10010</v>
       </c>
       <c r="N12" t="n">
-        <v>15.76</v>
+        <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>129312554600</v>
+        <v>360914833410</v>
       </c>
       <c r="P12" t="n">
-        <v>164700</v>
+        <v>22450</v>
       </c>
       <c r="Q12" t="n">
-        <v>87700</v>
+        <v>1760</v>
       </c>
       <c r="R12" t="n">
-        <v>-3000</v>
+        <v>181000</v>
       </c>
       <c r="S12" t="n">
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>합병 반대 의견이 존재하나, 정유 및 배터리 섹터의 슈퍼 사이클 기대감도 일부 언급. 주가 하락에 대한 우려와 상승 가능성에 대한 논의 혼재.</t>
+          <t>아이온큐 급등에 따른 광통신 테마 기대감. 기타법인 매수 유입.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['합병', '정유']</t>
+          <t>['광통신', '아이온큐', '기타법인']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10610</v>
+        <v>141700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+3.66%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.26</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="F13" t="n">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="H13" t="n">
-        <v>17.93</v>
+        <v>15.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10270</v>
+        <v>136700</v>
       </c>
       <c r="K13" t="n">
-        <v>11000</v>
+        <v>139500</v>
       </c>
       <c r="L13" t="n">
-        <v>11650</v>
+        <v>144100</v>
       </c>
       <c r="M13" t="n">
-        <v>10010</v>
+        <v>138200</v>
       </c>
       <c r="N13" t="n">
-        <v>17.67</v>
+        <v>15.76</v>
       </c>
       <c r="O13" t="n">
-        <v>359572334330</v>
+        <v>132774710700</v>
       </c>
       <c r="P13" t="n">
-        <v>22450</v>
+        <v>164700</v>
       </c>
       <c r="Q13" t="n">
-        <v>1760</v>
+        <v>87700</v>
       </c>
       <c r="R13" t="n">
-        <v>181000</v>
+        <v>-3000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아이온큐 급등에 따른 광통신 테마 기대감. 기타법인 매수 유입.</t>
+          <t>합병 반대 의견과 함께 주가 변동성에 대한 언급이 있으며, 정유 및 배터리 사업에 대한 긍정적 전망도 일부 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', '아이온큐', '기타법인']</t>
+          <t>['합병', '정유', '배터리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14960</v>
+        <v>14980</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.05%</t>
+          <t>'+2.18%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>105</v>
       </c>
       <c r="G14" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>67437556330</v>
+        <v>67804880910</v>
       </c>
       <c r="P14" t="n">
         <v>36200</v>
@@ -1759,184 +1759,184 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19130</v>
+        <v>17550</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>-2.35</v>
       </c>
       <c r="E15" t="n">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="G15" t="n">
-        <v>472</v>
+        <v>353</v>
       </c>
       <c r="H15" t="n">
-        <v>10.53</v>
+        <v>0.35</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18760</v>
+        <v>17200</v>
       </c>
       <c r="K15" t="n">
-        <v>18440</v>
+        <v>17220</v>
       </c>
       <c r="L15" t="n">
-        <v>19330</v>
+        <v>18390</v>
       </c>
       <c r="M15" t="n">
-        <v>18120</v>
+        <v>16600</v>
       </c>
       <c r="N15" t="n">
-        <v>10.55</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>82855768575</v>
+        <v>199678769700</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>30550</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>6100</v>
       </c>
       <c r="R15" t="n">
-        <v>23000</v>
+        <v>-33000</v>
       </c>
       <c r="S15" t="n">
-        <v>29000</v>
+        <v>2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
+          <t>미국 양자 보안주 강세 속에서 신고가를 기록했으나, 주포의 움직임에 대한 의문과 재미없는 흐름 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '공시', '흐름']</t>
+          <t>['양자 보안', '신고가', '주포']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17510</v>
+        <v>19130</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.80%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2.35</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="F16" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>350</v>
+        <v>475</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35</v>
+        <v>10.53</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17200</v>
+        <v>18760</v>
       </c>
       <c r="K16" t="n">
-        <v>17220</v>
+        <v>18440</v>
       </c>
       <c r="L16" t="n">
-        <v>18390</v>
+        <v>19330</v>
       </c>
       <c r="M16" t="n">
-        <v>16600</v>
+        <v>18120</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>10.55</v>
       </c>
       <c r="O16" t="n">
-        <v>198935439450</v>
+        <v>83511372805</v>
       </c>
       <c r="P16" t="n">
-        <v>30550</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>6100</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>-33000</v>
+        <v>23000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>양자 보안 관련 테마주로 언급되며 신고가 달성. 일부 긍정적인 흐름에 대한 기대와 함께 주가 움직임에 대한 아쉬움도 공존.</t>
+          <t>긍정적인 흐름과 대박 공시 기대감 형성. "대차해지" 독려 운동 활발.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['양자보안', '신고가']</t>
+          <t>['대차해지', '공시', '흐름']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10130</v>
+        <v>10120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+1.30%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>115</v>
       </c>
       <c r="F17" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>163977568895</v>
+        <v>164522419575</v>
       </c>
       <c r="P17" t="n">
         <v>15960</v>
@@ -2050,13 +2050,13 @@
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>46379308410</v>
+        <v>46596272010</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1688000</v>
+        <v>248500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.53%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="G19" t="n">
-        <v>1471</v>
+        <v>1440</v>
       </c>
       <c r="H19" t="n">
-        <v>50.27</v>
+        <v>46.57</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1697000</v>
+        <v>249000</v>
       </c>
       <c r="K19" t="n">
-        <v>1690000</v>
+        <v>248000</v>
       </c>
       <c r="L19" t="n">
-        <v>1729000</v>
+        <v>252000</v>
       </c>
       <c r="M19" t="n">
-        <v>1671000</v>
+        <v>246000</v>
       </c>
       <c r="N19" t="n">
-        <v>50.47</v>
+        <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>4089931805500</v>
+        <v>2761175232000</v>
       </c>
       <c r="P19" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>325000</v>
+        <v>75900</v>
       </c>
       <c r="R19" t="n">
-        <v>-297000</v>
+        <v>-368000</v>
       </c>
       <c r="S19" t="n">
-        <v>-104000</v>
+        <v>-565000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>금리 인상, AI 이슈 등 거시 경제 및 산업 불확실성에 대한 우려가 지배적. 투자 심리 불안정 및 하락 가능성에 대한 논의가 많음.</t>
+          <t>네이버 증권 화면 변경에 대한 불만과 금리 인상에 대한 다양한 의견이 혼재하는 게시글.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['금리인상', 'AI이슈']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247500</v>
+        <v>1690000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.60%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E20" t="n">
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="G20" t="n">
-        <v>1407</v>
+        <v>1453</v>
       </c>
       <c r="H20" t="n">
-        <v>46.57</v>
+        <v>50.27</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>249000</v>
+        <v>1697000</v>
       </c>
       <c r="K20" t="n">
-        <v>248000</v>
+        <v>1690000</v>
       </c>
       <c r="L20" t="n">
-        <v>252000</v>
+        <v>1729000</v>
       </c>
       <c r="M20" t="n">
-        <v>246000</v>
+        <v>1671000</v>
       </c>
       <c r="N20" t="n">
-        <v>46.64</v>
+        <v>50.47</v>
       </c>
       <c r="O20" t="n">
-        <v>2522749670500</v>
+        <v>4334937865500</v>
       </c>
       <c r="P20" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q20" t="n">
-        <v>75900</v>
+        <v>325000</v>
       </c>
       <c r="R20" t="n">
-        <v>-368000</v>
+        <v>-297000</v>
       </c>
       <c r="S20" t="n">
-        <v>-565000</v>
+        <v>-104000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치 관련 언급이 주를 이루며, 일부 증시 환경 변화에 대한 언급이 있으나 구체적인 분석은 부족함. 투자 심리에는 부정적 영향을 줄 수 있음.</t>
+          <t>금리, AI, 중국 메모리 등 다양한 악재 속에 하락세를 보이는 SK하이닉스에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['금리 인상', 'AI 이슈', '메모리']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2326,13 +2326,13 @@
         <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F21" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G21" t="n">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="H21" t="n">
         <v>23.45</v>
@@ -2358,7 +2358,7 @@
         <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>170612923950</v>
+        <v>176869664750</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2418,13 +2418,13 @@
         <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F22" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>109657552000</v>
+        <v>112357589500</v>
       </c>
       <c r="P22" t="n">
         <v>426000</v>
@@ -2516,7 +2516,7 @@
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>65668290970</v>
+        <v>65990386030</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>머니투데이 방송 노출 효과 및 광통신 테마 기대. AI, 금리 등 거시 변수.</t>
+          <t>머니투데이 방송 홍보 효과로 상승 기대감이 있으며, 광통신 테마로의 움직임 가능성 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '테마', 'AI']</t>
+          <t>['대한광통신', '홍보', '광통신']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8620</v>
+        <v>8610</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F24" t="n">
         <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="H24" t="n">
         <v>27.16</v>
@@ -2634,7 +2634,7 @@
         <v>27.16</v>
       </c>
       <c r="O24" t="n">
-        <v>28732683230</v>
+        <v>29941079510</v>
       </c>
       <c r="P24" t="n">
         <v>17950</v>
@@ -2700,7 +2700,7 @@
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>76415249547</v>
+        <v>76603179227</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20750</v>
+        <v>20700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F26" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G26" t="n">
-        <v>642</v>
+        <v>670</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>75905273150</v>
+        <v>82202151050</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12억 달러 수주 공시에도 불구하고 주가 하락. 시장은 수주를 악재로 인식하는 분위기. 개인 투자자들의 불만 표출.</t>
+          <t>12억 달러 수주 공시에도 불구하고 주가 하락에 대한 실망감과 의문 제기.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['수주 공시', '조선업', '주가 하락']</t>
+          <t>['수주 공시', '주가 하락', '자사주 소각']</t>
         </is>
       </c>
       <c r="X26" t="n">

--- a/data/trending_integrated_20260915_15.xlsx
+++ b/data/trending_integrated_20260915_15.xlsx
@@ -584,7 +584,7 @@
         <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="H2" t="n">
         <v>1.34</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>133872213985</v>
+        <v>133874602945</v>
       </c>
       <c r="P2" t="n">
         <v>5100</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>거래량 급증과 함께 광통신, 양자 관련 테마주로 부각되며 큰 폭의 상승세를 보임.</t>
+          <t>광통신, 양자, AI 등 첨단 소재 테마 관련 급등 및 1만원 목표가 제시. 주포 및 거래량 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['양자', '광통신', '테마주']</t>
+          <t>['광통신', '양자', 'AI']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.54</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F3" t="n">
         <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="H3" t="n">
         <v>3.02</v>
@@ -702,7 +702,7 @@
         <v>3.56</v>
       </c>
       <c r="O3" t="n">
-        <v>67015082895</v>
+        <v>67104893125</v>
       </c>
       <c r="P3" t="n">
         <v>11370</v>
@@ -768,7 +768,7 @@
         <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H4" t="n">
         <v>2.68</v>
@@ -794,7 +794,7 @@
         <v>2.99</v>
       </c>
       <c r="O4" t="n">
-        <v>49002235299</v>
+        <v>49008192269</v>
       </c>
       <c r="P4" t="n">
         <v>8980</v>
@@ -854,13 +854,13 @@
         <v>-0.06</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H5" t="n">
         <v>1.19</v>
@@ -886,7 +886,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>221969096530</v>
+        <v>221997000560</v>
       </c>
       <c r="P5" t="n">
         <v>25050</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>탈모 치료제 특허 및 세계 최초 타이틀에 대한 기대감으로 급등했으나, 변동성도 큰 모습을 보임.</t>
+          <t>싸이모신 알파1, 탈모 치료제 관련 특허 및 품절주 가능성 언급. 로봇주 비교 및 주포 활동 분석.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['탈모 치료제', '특허', '품절주']</t>
+          <t>['탈모치료제', '품절주', '특허']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -952,7 +952,7 @@
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H6" t="n">
         <v>4.9</v>
@@ -978,7 +978,7 @@
         <v>4.89</v>
       </c>
       <c r="O6" t="n">
-        <v>227979221250</v>
+        <v>228065443350</v>
       </c>
       <c r="P6" t="n">
         <v>50600</v>
@@ -1038,13 +1038,13 @@
         <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
         <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H7" t="n">
         <v>0.83</v>
@@ -1070,7 +1070,7 @@
         <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>159149202156</v>
+        <v>159168790796</v>
       </c>
       <c r="P7" t="n">
         <v>4335</v>
@@ -1130,13 +1130,13 @@
         <v>-0.18</v>
       </c>
       <c r="E8" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G8" t="n">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="H8" t="n">
         <v>13.97</v>
@@ -1162,7 +1162,7 @@
         <v>14.15</v>
       </c>
       <c r="O8" t="n">
-        <v>99037159425</v>
+        <v>99043196625</v>
       </c>
       <c r="P8" t="n">
         <v>108900</v>
@@ -1222,13 +1222,13 @@
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F9" t="n">
         <v>129</v>
       </c>
       <c r="G9" t="n">
-        <v>1108</v>
+        <v>1156</v>
       </c>
       <c r="H9" t="n">
         <v>17.5</v>
@@ -1254,7 +1254,7 @@
         <v>17.55</v>
       </c>
       <c r="O9" t="n">
-        <v>19930916700</v>
+        <v>19931922650</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 승인 기대감 및 주가 변동성. 기관/외인 매도.</t>
+          <t>담관암 FDA 승인에 대한 기대와 불확실성이 공존하며, 기관/외인 매도 및 주가 하락에 대한 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '기관외인']</t>
+          <t>['담관암', 'FDA', '승인']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H10" t="n">
         <v>14.93</v>
@@ -1346,7 +1346,7 @@
         <v>15.06</v>
       </c>
       <c r="O10" t="n">
-        <v>61079008375</v>
+        <v>61080906475</v>
       </c>
       <c r="P10" t="n">
         <v>50400</v>
@@ -1438,7 +1438,7 @@
         <v>10.69</v>
       </c>
       <c r="O11" t="n">
-        <v>130307040765</v>
+        <v>130337280645</v>
       </c>
       <c r="P11" t="n">
         <v>23550</v>
@@ -1498,13 +1498,13 @@
         <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G12" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="H12" t="n">
         <v>17.93</v>
@@ -1530,7 +1530,7 @@
         <v>17.67</v>
       </c>
       <c r="O12" t="n">
-        <v>360914833410</v>
+        <v>360990615350</v>
       </c>
       <c r="P12" t="n">
         <v>22450</v>
@@ -1590,13 +1590,13 @@
         <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H13" t="n">
         <v>15.81</v>
@@ -1622,7 +1622,7 @@
         <v>15.76</v>
       </c>
       <c r="O13" t="n">
-        <v>132774710700</v>
+        <v>132781087200</v>
       </c>
       <c r="P13" t="n">
         <v>164700</v>
@@ -1682,13 +1682,13 @@
         <v>-1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>1.17</v>
       </c>
       <c r="O14" t="n">
-        <v>67804880910</v>
+        <v>67858988670</v>
       </c>
       <c r="P14" t="n">
         <v>36200</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>중동 지역의 지정학적 이슈로 인한 유가 급등 가능성 및 관련 수혜 기대감. 긍정적인 흐름 전망. 유가 관련 논의 활발.</t>
+          <t>이란 관련 지정학적 리스크와 유가 급등 가능성 언급. 외인 동향 및 목표가 제시.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '중동']</t>
+          <t>['유가', '이란', '지정학적']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1777,10 +1777,10 @@
         <v>227</v>
       </c>
       <c r="F15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H15" t="n">
         <v>0.35</v>
@@ -1806,7 +1806,7 @@
         <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>199678769700</v>
+        <v>199692739500</v>
       </c>
       <c r="P15" t="n">
         <v>30550</v>
@@ -1872,7 +1872,7 @@
         <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="H16" t="n">
         <v>10.53</v>
@@ -1898,7 +1898,7 @@
         <v>10.55</v>
       </c>
       <c r="O16" t="n">
-        <v>83511372805</v>
+        <v>83536031375</v>
       </c>
       <c r="P16" t="n">
         <v>40350</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
@@ -1990,7 +1990,7 @@
         <v>0.6</v>
       </c>
       <c r="O17" t="n">
-        <v>164522419575</v>
+        <v>164549581655</v>
       </c>
       <c r="P17" t="n">
         <v>15960</v>
@@ -2050,13 +2050,13 @@
         <v>-0.97</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="H18" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>46596272010</v>
+        <v>46610996610</v>
       </c>
       <c r="P18" t="n">
         <v>10360</v>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G19" t="n">
-        <v>1440</v>
+        <v>1482</v>
       </c>
       <c r="H19" t="n">
         <v>46.57</v>
@@ -2174,7 +2174,7 @@
         <v>46.64</v>
       </c>
       <c r="O19" t="n">
-        <v>2761175232000</v>
+        <v>2761372541000</v>
       </c>
       <c r="P19" t="n">
         <v>374500</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>네이버 증권 화면 변경에 대한 불만과 금리 인상에 대한 다양한 의견이 혼재하는 게시글.</t>
+          <t>네이버 증권 화면 변경에 대한 불만과 함께 금리 인상 선반영 및 정치 관련 언급이 혼재된 분석.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['금리인상', '네이버증권', '분석']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="G20" t="n">
-        <v>1453</v>
+        <v>1443</v>
       </c>
       <c r="H20" t="n">
         <v>50.27</v>
@@ -2266,7 +2266,7 @@
         <v>50.47</v>
       </c>
       <c r="O20" t="n">
-        <v>4334937865500</v>
+        <v>4335152495500</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>금리, AI, 중국 메모리 등 다양한 악재 속에 하락세를 보이는 SK하이닉스에 대한 부정적 전망.</t>
+          <t>JP모건 AI 인프라 대출 중단, 금리 이슈, 정치 관련 언급과 함께 주가 하락에 대한 부정적 전망 제시.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['금리 인상', 'AI 이슈', '메모리']</t>
+          <t>['금리', 'AI', '주가하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2326,13 +2326,13 @@
         <v>-0.11</v>
       </c>
       <c r="E21" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F21" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G21" t="n">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="H21" t="n">
         <v>23.45</v>
@@ -2358,7 +2358,7 @@
         <v>23.56</v>
       </c>
       <c r="O21" t="n">
-        <v>176869664750</v>
+        <v>176889232150</v>
       </c>
       <c r="P21" t="n">
         <v>139200</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전 사업 확대 기대감 및 수주 증가 전망. 에너지 독립 관련 수혜.</t>
+          <t>원전 사업 확대 기대감과 함께 10만 돌파 가능성 언급. 에너지 독립 및 ETF 관련 분석.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '수주', '에너지독립']</t>
+          <t>['원전', '에너지', 'ETF']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>0.15</v>
       </c>
       <c r="E22" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F22" t="n">
         <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>1076</v>
+        <v>1092</v>
       </c>
       <c r="H22" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>7.05</v>
       </c>
       <c r="O22" t="n">
-        <v>112357589500</v>
+        <v>112385624500</v>
       </c>
       <c r="P22" t="n">
         <v>426000</v>
@@ -2510,13 +2510,13 @@
         <v>-0.08</v>
       </c>
       <c r="E23" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
         <v>69</v>
       </c>
       <c r="G23" t="n">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="H23" t="n">
         <v>1.8</v>
@@ -2542,7 +2542,7 @@
         <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>65990386030</v>
+        <v>66017294450</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>머니투데이 방송 홍보 효과로 상승 기대감이 있으며, 광통신 테마로의 움직임 가능성 언급.</t>
+          <t>머니투데이 방송 노출 및 15,000원 이상 목표가 제시. 광전자 테마 비교 및 차익 실현 가능성 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['대한광통신', '홍보', '광통신']</t>
+          <t>['광통신', '목표가', '방송']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F24" t="n">
         <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="H24" t="n">
         <v>27.16</v>
@@ -2634,7 +2634,7 @@
         <v>27.16</v>
       </c>
       <c r="O24" t="n">
-        <v>29941079510</v>
+        <v>29981124620</v>
       </c>
       <c r="P24" t="n">
         <v>17950</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>목표주가 하향 및 실적 부진 우려. 공매도 세력 활동.</t>
+          <t>대표이사 사퇴 요구와 함께 목표 주가 하향, 저평가 논란 및 공매도 관련 언급이 혼재된 분석.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['목표주가', '실적', '공매도']</t>
+          <t>['목표주가', '공매도', '저평가']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2694,13 +2694,13 @@
         <v>0.18</v>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
         <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="H25" t="n">
         <v>0.77</v>
@@ -2726,7 +2726,7 @@
         <v>0.59</v>
       </c>
       <c r="O25" t="n">
-        <v>76603179227</v>
+        <v>76614191987</v>
       </c>
       <c r="P25" t="n">
         <v>8100</v>
@@ -2786,13 +2786,13 @@
         <v>0.09</v>
       </c>
       <c r="E26" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F26" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G26" t="n">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="H26" t="n">
         <v>28.9</v>
@@ -2818,7 +2818,7 @@
         <v>28.81</v>
       </c>
       <c r="O26" t="n">
-        <v>82202151050</v>
+        <v>82205566550</v>
       </c>
       <c r="P26" t="n">
         <v>35350</v>
